--- a/data/trans_orig/IQ21A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ21A-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de veces que han estado hospitalizados a lo largo de estos últimos 12 meses</t>
+          <t>Menores según el número de veces que han estado hospitalizados a lo largo de estos últimos 12 meses (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,77</t>
+          <t>1,0; 1,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,42</t>
+          <t>1,0; 1,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,85</t>
+          <t>1,0; 1,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,72</t>
+          <t>1,0; 1,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,63</t>
+          <t>1,0; 1,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,42</t>
+          <t>1,0; 1,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,33</t>
+          <t>1,0; 1,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,44</t>
+          <t>1,0; 1,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,37</t>
+          <t>1,04; 1,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,1</t>
+          <t>1,0; 2,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,28</t>
+          <t>1,0; 1,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 34,88</t>
+          <t>1,0; 36,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,17</t>
+          <t>1,0; 1,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,22</t>
+          <t>1,03; 1,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 22,09</t>
+          <t>1,11; 22,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1281,12 +1281,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,68</t>
+          <t>1,0; 1,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,57</t>
+          <t>1,0; 1,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,76</t>
+          <t>1,13; 4,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,75</t>
+          <t>1,19; 2,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,09</t>
+          <t>1,0; 4,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,3</t>
+          <t>1,08; 3,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,24</t>
+          <t>1,19; 2,21</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,78</t>
+          <t>1,04; 2,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,47</t>
+          <t>1,0; 1,46</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1556,17 +1556,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,22</t>
+          <t>1,0; 1,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,31</t>
+          <t>1,05; 1,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,32</t>
+          <t>1,03; 1,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,7</t>
+          <t>1,06; 1,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,47</t>
+          <t>1,05; 1,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,71</t>
+          <t>1,09; 11,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1596,17 +1596,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,47</t>
+          <t>1,06; 1,44</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,34</t>
+          <t>1,08; 1,35</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,64</t>
+          <t>1,14; 6,1</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">

--- a/data/trans_orig/IQ21A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ21A-Clase-trans_orig.xlsx
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,73</t>
+          <t>1,0; 1,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,43</t>
+          <t>1,0; 1,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,78</t>
+          <t>1,0; 1,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,71</t>
+          <t>1,0; 1,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,62</t>
+          <t>1,0; 1,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,36</t>
+          <t>1,0; 1,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,43</t>
+          <t>1,0; 1,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,41</t>
+          <t>1,04; 1,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,18</t>
+          <t>1,0; 2,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,31</t>
+          <t>1,0; 1,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 36,59</t>
+          <t>1,0; 34,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,21</t>
+          <t>1,0; 1,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,24</t>
+          <t>1,03; 1,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 22,62</t>
+          <t>1,11; 22,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1281,12 +1281,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,67</t>
+          <t>1,0; 1,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,55</t>
+          <t>1,0; 1,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,68</t>
+          <t>1,14; 4,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,69</t>
+          <t>1,21; 2,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,06</t>
+          <t>1,0; 4,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,68</t>
+          <t>1,08; 3,73</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,21</t>
+          <t>1,22; 2,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,95</t>
+          <t>1,0; 2,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1556,17 +1556,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,23</t>
+          <t>1,0; 1,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,29</t>
+          <t>1,05; 1,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,32</t>
+          <t>1,03; 1,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,71</t>
+          <t>1,06; 1,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,48</t>
+          <t>1,06; 1,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 11,27</t>
+          <t>1,12; 11,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1596,17 +1596,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,44</t>
+          <t>1,05; 1,5</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,35</t>
+          <t>1,08; 1,34</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,1</t>
+          <t>1,13; 6,05</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
